--- a/T11_CWB.xlsx
+++ b/T11_CWB.xlsx
@@ -554,7 +554,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>T11 CWB Omnia Combined Auto Daily Test Report</t>
+          <t>T11 Pre_Proto_1 Combined Auto Daily Test Report</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -568,7 +568,7 @@
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>N/A 04:00:00 AM</t>
+          <t>2025/12/17 04:00:00 AM</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -588,40 +588,40 @@
       <c r="B3" s="3" t="n"/>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>Jade-EVT_T01a-Awa</t>
+          <t>T11 Pre_Proto_1_T01a-Awa</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>Jade-EVT_T02a-Awa</t>
+          <t>T11 Pre_Proto_1_T02a-Awa</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
         <is>
-          <t>Jade-EVT_T03a-Awa</t>
+          <t>T11 Pre_Proto_1_T03a-Awa</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>WiPAS Version</t>
+          <t>Version</t>
         </is>
       </c>
       <c r="B4" s="3" t="n"/>
       <c r="C4" s="5" t="inlineStr">
         <is>
+          <t>V1.0.4.1</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
           <t>V1.0.4.2</t>
         </is>
       </c>
-      <c r="D4" s="5" t="inlineStr">
+      <c r="E4" s="5" t="inlineStr">
         <is>
           <t>V1.0.3.7</t>
-        </is>
-      </c>
-      <c r="E4" s="5" t="inlineStr">
-        <is>
-          <t>V1.0.4.1</t>
         </is>
       </c>
     </row>
@@ -1264,12 +1264,12 @@
       <c r="B4" s="3" t="n"/>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>V1.0.3.7</t>
+          <t>V1.0.4.1</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>V1.0.3.7</t>
+          <t>V1.0.4.1</t>
         </is>
       </c>
     </row>

--- a/T11_CWB.xlsx
+++ b/T11_CWB.xlsx
@@ -611,17 +611,17 @@
       <c r="B4" s="3" t="n"/>
       <c r="C4" s="5" t="inlineStr">
         <is>
+          <t>V1.0.4.2</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>V1.0.3.7</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
           <t>V1.0.4.1</t>
-        </is>
-      </c>
-      <c r="D4" s="5" t="inlineStr">
-        <is>
-          <t>V1.0.4.2</t>
-        </is>
-      </c>
-      <c r="E4" s="5" t="inlineStr">
-        <is>
-          <t>V1.0.3.7</t>
         </is>
       </c>
     </row>
@@ -697,7 +697,7 @@
         </is>
       </c>
       <c r="B8" s="8" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C8" s="8" t="n">
         <v>5</v>
@@ -716,7 +716,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C9" s="7" t="n">
         <v>3</v>
@@ -773,7 +773,7 @@
         </is>
       </c>
       <c r="B12" s="12" t="n">
-        <v>0.8461538461538461</v>
+        <v>1</v>
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         </is>
       </c>
       <c r="B13" s="13" t="n">
-        <v>0.3076923076923077</v>
+        <v>0.4615384615384616</v>
       </c>
       <c r="C13" s="7" t="inlineStr">
         <is>
@@ -1212,7 +1212,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Jade EVT T01a-Awa Daily Test Report</t>
+          <t>T11 T01a-Awa Daily Test Report</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1246,12 +1246,12 @@
       <c r="B3" s="3" t="n"/>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>Jade-EVT_T01a-Awa</t>
+          <t>T11_Pre_Proto_1_T01a-Awa</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>Jade-EVT_T01a-Awa</t>
+          <t>T11_Pre_Proto_1_T01a-Awa</t>
         </is>
       </c>
     </row>
@@ -1264,12 +1264,12 @@
       <c r="B4" s="3" t="n"/>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>V1.0.4.1</t>
+          <t>V1.0.3.7</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>V1.0.4.1</t>
+          <t>V1.0.3.7</t>
         </is>
       </c>
     </row>
@@ -1613,7 +1613,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Jade EVT T02a-Awa Daily Test Report</t>
+          <t>T11 T02a-Awa Daily Test Report</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1647,12 +1647,12 @@
       <c r="B3" s="3" t="n"/>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>Jade-EVT_T02a-Awa</t>
+          <t>T11_Pre_Proto_1_T02a-Awa</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>Jade-EVT_T02a-Awa</t>
+          <t>T11_Pre_Proto_1_T02a-Awa</t>
         </is>
       </c>
     </row>
@@ -2006,7 +2006,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Jade EVT T03a-Awa Daily Test Report</t>
+          <t>T11 T03a-Awa Daily Test Report</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2040,7 +2040,7 @@
       <c r="B3" s="3" t="n"/>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>Jade-EVT_T03a-Awa</t>
+          <t>T11_Pre_Proto_1_T03a-Awa</t>
         </is>
       </c>
     </row>

--- a/T11_CWB.xlsx
+++ b/T11_CWB.xlsx
@@ -539,7 +539,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R28"/>
+  <dimension ref="A1:R30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -611,17 +611,17 @@
       <c r="B4" s="3" t="n"/>
       <c r="C4" s="5" t="inlineStr">
         <is>
+          <t>V1.0.4.1</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
           <t>V1.0.4.2</t>
         </is>
       </c>
-      <c r="D4" s="5" t="inlineStr">
+      <c r="E4" s="5" t="inlineStr">
         <is>
           <t>V1.0.3.7</t>
-        </is>
-      </c>
-      <c r="E4" s="5" t="inlineStr">
-        <is>
-          <t>V1.0.4.1</t>
         </is>
       </c>
     </row>
@@ -678,16 +678,16 @@
         </is>
       </c>
       <c r="B7" s="7" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C7" s="7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D7" s="7" t="n">
         <v>4</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8">
@@ -773,21 +773,21 @@
         </is>
       </c>
       <c r="B12" s="12" t="n">
-        <v>1</v>
+        <v>0.8666666666666667</v>
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
+          <t>83.33%</t>
+        </is>
+      </c>
+      <c r="D12" s="8" t="inlineStr">
+        <is>
           <t>100.00%</t>
         </is>
       </c>
-      <c r="D12" s="8" t="inlineStr">
-        <is>
-          <t>100.00%</t>
-        </is>
-      </c>
       <c r="E12" s="8" t="inlineStr">
         <is>
-          <t>100.00%</t>
+          <t>80.00%</t>
         </is>
       </c>
     </row>
@@ -798,11 +798,11 @@
         </is>
       </c>
       <c r="B13" s="13" t="n">
-        <v>0.4615384615384616</v>
+        <v>0.4</v>
       </c>
       <c r="C13" s="7" t="inlineStr">
         <is>
-          <t>60.00%</t>
+          <t>50.00%</t>
         </is>
       </c>
       <c r="D13" s="7" t="inlineStr">
@@ -812,7 +812,7 @@
       </c>
       <c r="E13" s="7" t="inlineStr">
         <is>
-          <t>50.00%</t>
+          <t>40.00%</t>
         </is>
       </c>
     </row>
@@ -823,21 +823,21 @@
         </is>
       </c>
       <c r="B14" s="13" t="n">
-        <v>0.5384615384615384</v>
+        <v>0.4666666666666667</v>
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
+          <t>33.33%</t>
+        </is>
+      </c>
+      <c r="D14" s="7" t="inlineStr">
+        <is>
+          <t>75.00%</t>
+        </is>
+      </c>
+      <c r="E14" s="7" t="inlineStr">
+        <is>
           <t>40.00%</t>
-        </is>
-      </c>
-      <c r="D14" s="7" t="inlineStr">
-        <is>
-          <t>75.00%</t>
-        </is>
-      </c>
-      <c r="E14" s="7" t="inlineStr">
-        <is>
-          <t>50.00%</t>
         </is>
       </c>
     </row>
@@ -848,21 +848,21 @@
         </is>
       </c>
       <c r="B15" s="14" t="n">
-        <v>0.1538461538461539</v>
+        <v>0.1333333333333333</v>
       </c>
       <c r="C15" s="10" t="inlineStr">
         <is>
+          <t>16.67%</t>
+        </is>
+      </c>
+      <c r="D15" s="10" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="E15" s="10" t="inlineStr">
+        <is>
           <t>20.00%</t>
-        </is>
-      </c>
-      <c r="D15" s="10" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="E15" s="10" t="inlineStr">
-        <is>
-          <t>25.00%</t>
         </is>
       </c>
       <c r="F15" s="11" t="n"/>
@@ -879,133 +879,91 @@
       <c r="Q15" s="11" t="n"/>
       <c r="R15" s="11" t="n"/>
     </row>
-    <row r="16">
-      <c r="A16" s="7" t="inlineStr">
-        <is>
-          <t>Test Waive Quantity</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" s="15" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>Retest OK Quantity</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="15" customHeight="1">
+      <c r="A19" s="15" t="inlineStr">
         <is>
           <t>NO.</t>
         </is>
       </c>
-      <c r="B17" s="15" t="inlineStr">
+      <c r="B19" s="15" t="inlineStr">
         <is>
           <t>Retest Type</t>
         </is>
       </c>
-      <c r="C17" s="15" t="inlineStr">
+      <c r="C19" s="15" t="inlineStr">
         <is>
           <t>Retest Count</t>
         </is>
       </c>
-      <c r="D17" s="15" t="inlineStr">
+      <c r="D19" s="15" t="inlineStr">
         <is>
           <t>Percentage</t>
         </is>
       </c>
-      <c r="E17" s="15" t="inlineStr">
+      <c r="E19" s="15" t="inlineStr">
         <is>
           <t>Station ID</t>
         </is>
       </c>
-      <c r="F17" s="15" t="inlineStr">
+      <c r="F19" s="15" t="inlineStr">
         <is>
           <t>Station Count</t>
         </is>
       </c>
-      <c r="G17" s="15" t="inlineStr">
+      <c r="G19" s="15" t="inlineStr">
         <is>
           <t>Failing Tests</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="15" customHeight="1">
-      <c r="A18" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="B18" s="16" t="inlineStr">
+    <row r="20" ht="15" customHeight="1">
+      <c r="A20" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="B20" s="16" t="inlineStr">
         <is>
           <t>WIFI_TX-5180-HT20_MCS7-12</t>
         </is>
       </c>
-      <c r="C18" s="7" t="n">
+      <c r="C20" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="D18" s="7" t="inlineStr">
-        <is>
-          <t>23.08%</t>
-        </is>
-      </c>
-      <c r="E18" s="7" t="inlineStr">
+      <c r="D20" s="7" t="inlineStr">
+        <is>
+          <t>20.00%</t>
+        </is>
+      </c>
+      <c r="E20" s="7" t="inlineStr">
         <is>
           <t>ITJS-D24F-SMT01-CWB-01</t>
         </is>
       </c>
-      <c r="F18" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G18" s="17" t="inlineStr"/>
-    </row>
-    <row r="19" ht="15" customHeight="1">
-      <c r="A19" s="18" t="n"/>
-      <c r="B19" s="18" t="n"/>
-      <c r="C19" s="18" t="n"/>
-      <c r="D19" s="18" t="n"/>
-      <c r="E19" s="7" t="inlineStr">
+      <c r="F20" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G20" s="17" t="inlineStr"/>
+    </row>
+    <row r="21" ht="15" customHeight="1">
+      <c r="A21" s="18" t="n"/>
+      <c r="B21" s="18" t="n"/>
+      <c r="C21" s="18" t="n"/>
+      <c r="D21" s="18" t="n"/>
+      <c r="E21" s="7" t="inlineStr">
         <is>
           <t>ITJS-D24F-SMT01-CWB-02</t>
         </is>
       </c>
-      <c r="F19" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G19" s="18" t="n"/>
-    </row>
-    <row r="20" ht="15" customHeight="1">
-      <c r="A20" s="19" t="n"/>
-      <c r="B20" s="19" t="n"/>
-      <c r="C20" s="19" t="n"/>
-      <c r="D20" s="19" t="n"/>
-      <c r="E20" s="7" t="inlineStr">
-        <is>
-          <t>ITJS-D24F-SMT01-CWB-06</t>
-        </is>
-      </c>
-      <c r="F20" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G20" s="19" t="n"/>
-    </row>
-    <row r="21" ht="15" customHeight="1">
-      <c r="A21" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="B21" s="16" t="inlineStr">
-        <is>
-          <t>WIFI_TX-2412-OFDM-54M-14</t>
-        </is>
-      </c>
-      <c r="C21" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="D21" s="7" t="inlineStr">
-        <is>
-          <t>15.38%</t>
-        </is>
-      </c>
-      <c r="E21" s="7" t="inlineStr">
-        <is>
-          <t>ITJS-D24F-SMT01-CWB-02</t>
-        </is>
-      </c>
       <c r="F21" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="G21" s="17" t="inlineStr"/>
+      <c r="G21" s="18" t="n"/>
     </row>
     <row r="22" ht="15" customHeight="1">
       <c r="A22" s="19" t="n"/>
@@ -1014,7 +972,7 @@
       <c r="D22" s="19" t="n"/>
       <c r="E22" s="7" t="inlineStr">
         <is>
-          <t>ITJS-D24F-SMT01-CWB-05</t>
+          <t>ITJS-D24F-SMT01-CWB-06</t>
         </is>
       </c>
       <c r="F22" s="7" t="n">
@@ -1024,24 +982,24 @@
     </row>
     <row r="23" ht="15" customHeight="1">
       <c r="A23" s="7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B23" s="16" t="inlineStr">
         <is>
-          <t>WIFI_RX-2412-HT20_MCS7--70</t>
+          <t>WIFI_TX-2412-OFDM-54M-14</t>
         </is>
       </c>
       <c r="C23" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D23" s="7" t="inlineStr">
         <is>
-          <t>7.69%</t>
+          <t>13.33%</t>
         </is>
       </c>
       <c r="E23" s="7" t="inlineStr">
         <is>
-          <t>ITJS-D24F-SMT01-CWB-06</t>
+          <t>ITJS-D24F-SMT01-CWB-02</t>
         </is>
       </c>
       <c r="F23" s="7" t="n">
@@ -1050,39 +1008,27 @@
       <c r="G23" s="17" t="inlineStr"/>
     </row>
     <row r="24" ht="15" customHeight="1">
-      <c r="A24" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="B24" s="16" t="inlineStr">
-        <is>
-          <t>WIFI_RX-2412-HT20_MCS7--75</t>
-        </is>
-      </c>
-      <c r="C24" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="D24" s="7" t="inlineStr">
-        <is>
-          <t>7.69%</t>
-        </is>
-      </c>
+      <c r="A24" s="19" t="n"/>
+      <c r="B24" s="19" t="n"/>
+      <c r="C24" s="19" t="n"/>
+      <c r="D24" s="19" t="n"/>
       <c r="E24" s="7" t="inlineStr">
         <is>
-          <t>ITJS-D24F-SMT01-CWB-06</t>
+          <t>ITJS-D24F-SMT01-CWB-05</t>
         </is>
       </c>
       <c r="F24" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="G24" s="17" t="inlineStr"/>
+      <c r="G24" s="19" t="n"/>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" s="7" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B25" s="16" t="inlineStr">
         <is>
-          <t>WIFI_TX-2412-HT20_MCS7-13</t>
+          <t>WIFI_RX-2412-HT20_MCS7--70</t>
         </is>
       </c>
       <c r="C25" s="7" t="n">
@@ -1090,12 +1036,12 @@
       </c>
       <c r="D25" s="7" t="inlineStr">
         <is>
-          <t>7.69%</t>
+          <t>6.67%</t>
         </is>
       </c>
       <c r="E25" s="7" t="inlineStr">
         <is>
-          <t>ITJS-D24F-SMT01-CWB-04</t>
+          <t>ITJS-D24F-SMT01-CWB-06</t>
         </is>
       </c>
       <c r="F25" s="7" t="n">
@@ -1105,64 +1051,118 @@
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="B26" s="16" t="inlineStr">
+        <is>
+          <t>WIFI_RX-2412-HT20_MCS7--75</t>
+        </is>
+      </c>
+      <c r="C26" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D26" s="7" t="inlineStr">
+        <is>
+          <t>6.67%</t>
+        </is>
+      </c>
+      <c r="E26" s="7" t="inlineStr">
+        <is>
+          <t>ITJS-D24F-SMT01-CWB-06</t>
+        </is>
+      </c>
+      <c r="F26" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G26" s="17" t="inlineStr"/>
+    </row>
+    <row r="27" ht="15" customHeight="1">
+      <c r="A27" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="B27" s="16" t="inlineStr">
+        <is>
+          <t>WIFI_TX-2412-HT20_MCS7-13</t>
+        </is>
+      </c>
+      <c r="C27" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D27" s="7" t="inlineStr">
+        <is>
+          <t>6.67%</t>
+        </is>
+      </c>
+      <c r="E27" s="7" t="inlineStr">
+        <is>
+          <t>ITJS-D24F-SMT01-CWB-04</t>
+        </is>
+      </c>
+      <c r="F27" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G27" s="17" t="inlineStr"/>
+    </row>
+    <row r="28" ht="15" customHeight="1">
+      <c r="A28" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="B26" s="16" t="inlineStr">
+      <c r="B28" s="16" t="inlineStr">
         <is>
           <t>WIFI_TX-2442-OFDM-54M-14</t>
         </is>
       </c>
-      <c r="C26" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="D26" s="7" t="inlineStr">
-        <is>
-          <t>7.69%</t>
-        </is>
-      </c>
-      <c r="E26" s="7" t="inlineStr">
+      <c r="C28" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D28" s="7" t="inlineStr">
+        <is>
+          <t>6.67%</t>
+        </is>
+      </c>
+      <c r="E28" s="7" t="inlineStr">
         <is>
           <t>ITJS-D24F-SMT01-CWB-02</t>
         </is>
       </c>
-      <c r="F26" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G26" s="17" t="inlineStr"/>
-    </row>
-    <row r="27" ht="15" customHeight="1"/>
-    <row r="28" ht="15" customHeight="1">
-      <c r="A28" s="15" t="inlineStr">
+      <c r="F28" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G28" s="17" t="inlineStr"/>
+    </row>
+    <row r="29" ht="15" customHeight="1"/>
+    <row r="30" ht="15" customHeight="1">
+      <c r="A30" s="15" t="inlineStr">
         <is>
           <t>NO.</t>
         </is>
       </c>
-      <c r="B28" s="15" t="inlineStr">
-        <is>
-          <t>Retest Type</t>
-        </is>
-      </c>
-      <c r="C28" s="15" t="inlineStr">
-        <is>
-          <t>Retest Count</t>
-        </is>
-      </c>
-      <c r="D28" s="15" t="inlineStr">
+      <c r="B30" s="15" t="inlineStr">
+        <is>
+          <t>Fail Type</t>
+        </is>
+      </c>
+      <c r="C30" s="15" t="inlineStr">
+        <is>
+          <t>Fail Count</t>
+        </is>
+      </c>
+      <c r="D30" s="15" t="inlineStr">
         <is>
           <t>Percentage</t>
         </is>
       </c>
-      <c r="E28" s="15" t="inlineStr">
+      <c r="E30" s="15" t="inlineStr">
         <is>
           <t>Station ID</t>
         </is>
       </c>
-      <c r="F28" s="15" t="inlineStr">
+      <c r="F30" s="15" t="inlineStr">
         <is>
           <t>Station Count</t>
         </is>
       </c>
-      <c r="G28" s="15" t="inlineStr">
+      <c r="G30" s="15" t="inlineStr">
         <is>
           <t>Failing Tests</t>
         </is>
@@ -1171,21 +1171,21 @@
   </sheetData>
   <mergeCells count="16">
     <mergeCell ref="A4:B4"/>
-    <mergeCell ref="B18:B20"/>
-    <mergeCell ref="B21:B22"/>
-    <mergeCell ref="D18:D20"/>
+    <mergeCell ref="B23:B24"/>
+    <mergeCell ref="C23:C24"/>
+    <mergeCell ref="G23:G24"/>
+    <mergeCell ref="B20:B22"/>
     <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A21:A22"/>
+    <mergeCell ref="C20:C22"/>
+    <mergeCell ref="A20:A22"/>
     <mergeCell ref="A5:B5"/>
-    <mergeCell ref="C21:C22"/>
-    <mergeCell ref="D21:D22"/>
-    <mergeCell ref="G21:G22"/>
+    <mergeCell ref="D20:D22"/>
+    <mergeCell ref="G20:G22"/>
+    <mergeCell ref="A23:A24"/>
+    <mergeCell ref="D23:D24"/>
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A6:B6"/>
-    <mergeCell ref="A18:A20"/>
-    <mergeCell ref="G18:G20"/>
-    <mergeCell ref="C18:C20"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1197,7 +1197,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H20"/>
+  <dimension ref="A1:H22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -1264,12 +1264,12 @@
       <c r="B4" s="3" t="n"/>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>V1.0.3.7</t>
+          <t>V1.0.4.1</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>V1.0.3.7</t>
+          <t>V1.0.4.1</t>
         </is>
       </c>
     </row>
@@ -1316,13 +1316,13 @@
         </is>
       </c>
       <c r="B7" s="7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C7" s="7" t="n">
         <v>5</v>
       </c>
       <c r="D7" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -1396,7 +1396,7 @@
         </is>
       </c>
       <c r="B12" s="12" t="n">
-        <v>1</v>
+        <v>0.8332999999999999</v>
       </c>
       <c r="C12" s="12" t="n">
         <v>1</v>
@@ -1412,7 +1412,7 @@
         </is>
       </c>
       <c r="B13" s="13" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="C13" s="13" t="n">
         <v>0.6</v>
@@ -1428,7 +1428,7 @@
         </is>
       </c>
       <c r="B14" s="13" t="n">
-        <v>0.4</v>
+        <v>0.3333</v>
       </c>
       <c r="C14" s="13" t="n">
         <v>0.4</v>
@@ -1444,141 +1444,141 @@
         </is>
       </c>
       <c r="B15" s="14" t="n">
-        <v>0.2</v>
+        <v>0.1667</v>
       </c>
       <c r="C15" s="14" t="n">
         <v>0</v>
       </c>
       <c r="D15" s="14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="7" t="inlineStr">
-        <is>
-          <t>Test Waive Quantity</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" s="15" t="inlineStr">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>Retest OK Quantity</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="15" customHeight="1">
+      <c r="A19" s="15" t="inlineStr">
         <is>
           <t>NO.</t>
         </is>
       </c>
-      <c r="B17" s="15" t="inlineStr">
+      <c r="B19" s="15" t="inlineStr">
         <is>
           <t>Retest Type</t>
         </is>
       </c>
-      <c r="C17" s="15" t="inlineStr">
+      <c r="C19" s="15" t="inlineStr">
         <is>
           <t>Retest Count</t>
         </is>
       </c>
-      <c r="D17" s="15" t="inlineStr">
+      <c r="D19" s="15" t="inlineStr">
         <is>
           <t>Percentage</t>
         </is>
       </c>
-      <c r="E17" s="15" t="inlineStr">
+      <c r="E19" s="15" t="inlineStr">
         <is>
           <t>Station ID</t>
         </is>
       </c>
-      <c r="F17" s="15" t="inlineStr">
+      <c r="F19" s="15" t="inlineStr">
         <is>
           <t>Station Count</t>
         </is>
       </c>
-      <c r="G17" s="15" t="inlineStr">
+      <c r="G19" s="15" t="inlineStr">
         <is>
           <t>Failing Tests</t>
         </is>
       </c>
-    </row>
-    <row r="18" ht="15" customHeight="1">
-      <c r="A18" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="B18" s="16" t="inlineStr">
-        <is>
-          <t>WIFI_RX-2412-HT20_MCS7--70</t>
-        </is>
-      </c>
-      <c r="C18" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="D18" s="7" t="inlineStr">
-        <is>
-          <t>20.00%</t>
-        </is>
-      </c>
-      <c r="E18" s="7" t="inlineStr">
-        <is>
-          <t>ITJS-D24F-SMT01-CWB-06</t>
-        </is>
-      </c>
-      <c r="F18" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G18" s="17" t="inlineStr"/>
-    </row>
-    <row r="19" ht="15" customHeight="1">
-      <c r="A19" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="B19" s="16" t="inlineStr">
-        <is>
-          <t>WIFI_RX-2412-HT20_MCS7--75</t>
-        </is>
-      </c>
-      <c r="C19" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="D19" s="7" t="inlineStr">
-        <is>
-          <t>20.00%</t>
-        </is>
-      </c>
-      <c r="E19" s="7" t="inlineStr">
-        <is>
-          <t>ITJS-D24F-SMT01-CWB-06</t>
-        </is>
-      </c>
-      <c r="F19" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G19" s="17" t="inlineStr"/>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="B20" s="16" t="inlineStr">
+        <is>
+          <t>WIFI_RX-2412-HT20_MCS7--70</t>
+        </is>
+      </c>
+      <c r="C20" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D20" s="7" t="inlineStr">
+        <is>
+          <t>16.67%</t>
+        </is>
+      </c>
+      <c r="E20" s="7" t="inlineStr">
+        <is>
+          <t>ITJS-D24F-SMT01-CWB-06</t>
+        </is>
+      </c>
+      <c r="F20" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G20" s="17" t="inlineStr"/>
+    </row>
+    <row r="21" ht="15" customHeight="1">
+      <c r="A21" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="B21" s="16" t="inlineStr">
+        <is>
+          <t>WIFI_RX-2412-HT20_MCS7--75</t>
+        </is>
+      </c>
+      <c r="C21" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D21" s="7" t="inlineStr">
+        <is>
+          <t>16.67%</t>
+        </is>
+      </c>
+      <c r="E21" s="7" t="inlineStr">
+        <is>
+          <t>ITJS-D24F-SMT01-CWB-06</t>
+        </is>
+      </c>
+      <c r="F21" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G21" s="17" t="inlineStr"/>
+    </row>
+    <row r="22" ht="15" customHeight="1">
+      <c r="A22" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="B20" s="16" t="inlineStr">
+      <c r="B22" s="16" t="inlineStr">
         <is>
           <t>WIFI_TX-2412-OFDM-54M-14</t>
         </is>
       </c>
-      <c r="C20" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="D20" s="7" t="inlineStr">
-        <is>
-          <t>20.00%</t>
-        </is>
-      </c>
-      <c r="E20" s="7" t="inlineStr">
+      <c r="C22" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D22" s="7" t="inlineStr">
+        <is>
+          <t>16.67%</t>
+        </is>
+      </c>
+      <c r="E22" s="7" t="inlineStr">
         <is>
           <t>ITJS-D24F-SMT01-CWB-02</t>
         </is>
       </c>
-      <c r="F20" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G20" s="17" t="inlineStr"/>
-    </row>
-    <row r="21" ht="15" customHeight="1"/>
+      <c r="F22" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G22" s="17" t="inlineStr"/>
+    </row>
+    <row r="23" ht="15" customHeight="1"/>
   </sheetData>
   <mergeCells count="6">
     <mergeCell ref="A4:B4"/>
@@ -1598,7 +1598,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H20"/>
+  <dimension ref="A1:H22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -1854,131 +1854,131 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="7" t="inlineStr">
-        <is>
-          <t>Test Waive Quantity</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" s="15" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>Retest OK Quantity</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="15" customHeight="1">
+      <c r="A19" s="15" t="inlineStr">
         <is>
           <t>NO.</t>
         </is>
       </c>
-      <c r="B17" s="15" t="inlineStr">
+      <c r="B19" s="15" t="inlineStr">
         <is>
           <t>Retest Type</t>
         </is>
       </c>
-      <c r="C17" s="15" t="inlineStr">
+      <c r="C19" s="15" t="inlineStr">
         <is>
           <t>Retest Count</t>
         </is>
       </c>
-      <c r="D17" s="15" t="inlineStr">
+      <c r="D19" s="15" t="inlineStr">
         <is>
           <t>Percentage</t>
         </is>
       </c>
-      <c r="E17" s="15" t="inlineStr">
+      <c r="E19" s="15" t="inlineStr">
         <is>
           <t>Station ID</t>
         </is>
       </c>
-      <c r="F17" s="15" t="inlineStr">
+      <c r="F19" s="15" t="inlineStr">
         <is>
           <t>Station Count</t>
         </is>
       </c>
-      <c r="G17" s="15" t="inlineStr">
+      <c r="G19" s="15" t="inlineStr">
         <is>
           <t>Failing Tests</t>
         </is>
       </c>
-    </row>
-    <row r="18" ht="15" customHeight="1">
-      <c r="A18" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="B18" s="16" t="inlineStr">
-        <is>
-          <t>WIFI_TX-5180-HT20_MCS7-12</t>
-        </is>
-      </c>
-      <c r="C18" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="D18" s="7" t="inlineStr">
-        <is>
-          <t>50.00%</t>
-        </is>
-      </c>
-      <c r="E18" s="7" t="inlineStr">
-        <is>
-          <t>ITJS-D24F-SMT01-CWB-02</t>
-        </is>
-      </c>
-      <c r="F18" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G18" s="17" t="inlineStr"/>
-    </row>
-    <row r="19" ht="15" customHeight="1">
-      <c r="A19" s="19" t="n"/>
-      <c r="B19" s="19" t="n"/>
-      <c r="C19" s="19" t="n"/>
-      <c r="D19" s="19" t="n"/>
-      <c r="E19" s="7" t="inlineStr">
-        <is>
-          <t>ITJS-D24F-SMT01-CWB-06</t>
-        </is>
-      </c>
-      <c r="F19" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G19" s="19" t="n"/>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="B20" s="16" t="inlineStr">
+        <is>
+          <t>WIFI_TX-5180-HT20_MCS7-12</t>
+        </is>
+      </c>
+      <c r="C20" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="B20" s="16" t="inlineStr">
+      <c r="D20" s="7" t="inlineStr">
+        <is>
+          <t>50.00%</t>
+        </is>
+      </c>
+      <c r="E20" s="7" t="inlineStr">
+        <is>
+          <t>ITJS-D24F-SMT01-CWB-02</t>
+        </is>
+      </c>
+      <c r="F20" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G20" s="17" t="inlineStr"/>
+    </row>
+    <row r="21" ht="15" customHeight="1">
+      <c r="A21" s="19" t="n"/>
+      <c r="B21" s="19" t="n"/>
+      <c r="C21" s="19" t="n"/>
+      <c r="D21" s="19" t="n"/>
+      <c r="E21" s="7" t="inlineStr">
+        <is>
+          <t>ITJS-D24F-SMT01-CWB-06</t>
+        </is>
+      </c>
+      <c r="F21" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G21" s="19" t="n"/>
+    </row>
+    <row r="22" ht="15" customHeight="1">
+      <c r="A22" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="B22" s="16" t="inlineStr">
         <is>
           <t>WIFI_TX-2442-OFDM-54M-14</t>
         </is>
       </c>
-      <c r="C20" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="D20" s="7" t="inlineStr">
+      <c r="C22" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D22" s="7" t="inlineStr">
         <is>
           <t>25.00%</t>
         </is>
       </c>
-      <c r="E20" s="7" t="inlineStr">
+      <c r="E22" s="7" t="inlineStr">
         <is>
           <t>ITJS-D24F-SMT01-CWB-02</t>
         </is>
       </c>
-      <c r="F20" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G20" s="17" t="inlineStr"/>
-    </row>
-    <row r="21" ht="15" customHeight="1"/>
+      <c r="F22" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G22" s="17" t="inlineStr"/>
+    </row>
+    <row r="23" ht="15" customHeight="1"/>
   </sheetData>
   <mergeCells count="11">
     <mergeCell ref="A4:B4"/>
-    <mergeCell ref="D18:D19"/>
-    <mergeCell ref="B18:B19"/>
-    <mergeCell ref="G18:G19"/>
+    <mergeCell ref="C20:C21"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A5:B5"/>
+    <mergeCell ref="A20:A21"/>
+    <mergeCell ref="G20:G21"/>
+    <mergeCell ref="B20:B21"/>
     <mergeCell ref="A1:H1"/>
-    <mergeCell ref="C18:C19"/>
-    <mergeCell ref="A18:A19"/>
+    <mergeCell ref="D20:D21"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A6:B6"/>
   </mergeCells>
@@ -1992,7 +1992,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H20"/>
+  <dimension ref="A1:H22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -2053,7 +2053,7 @@
       <c r="B4" s="3" t="n"/>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>V1.0.4.2</t>
+          <t>V1.0.4.1</t>
         </is>
       </c>
     </row>
@@ -2090,10 +2090,10 @@
         </is>
       </c>
       <c r="B7" s="7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C7" s="7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8">
@@ -2155,10 +2155,10 @@
         </is>
       </c>
       <c r="B12" s="12" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="C12" s="12" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="13">
@@ -2168,10 +2168,10 @@
         </is>
       </c>
       <c r="B13" s="13" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="C13" s="13" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="14">
@@ -2181,10 +2181,10 @@
         </is>
       </c>
       <c r="B14" s="13" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="C14" s="13" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="15">
@@ -2194,138 +2194,138 @@
         </is>
       </c>
       <c r="B15" s="14" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="C15" s="14" t="n">
-        <v>0.25</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="7" t="inlineStr">
-        <is>
-          <t>Test Waive Quantity</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" s="15" t="inlineStr">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>Retest OK Quantity</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="15" customHeight="1">
+      <c r="A19" s="15" t="inlineStr">
         <is>
           <t>NO.</t>
         </is>
       </c>
-      <c r="B17" s="15" t="inlineStr">
+      <c r="B19" s="15" t="inlineStr">
         <is>
           <t>Retest Type</t>
         </is>
       </c>
-      <c r="C17" s="15" t="inlineStr">
+      <c r="C19" s="15" t="inlineStr">
         <is>
           <t>Retest Count</t>
         </is>
       </c>
-      <c r="D17" s="15" t="inlineStr">
+      <c r="D19" s="15" t="inlineStr">
         <is>
           <t>Percentage</t>
         </is>
       </c>
-      <c r="E17" s="15" t="inlineStr">
+      <c r="E19" s="15" t="inlineStr">
         <is>
           <t>Station ID</t>
         </is>
       </c>
-      <c r="F17" s="15" t="inlineStr">
+      <c r="F19" s="15" t="inlineStr">
         <is>
           <t>Station Count</t>
         </is>
       </c>
-      <c r="G17" s="15" t="inlineStr">
+      <c r="G19" s="15" t="inlineStr">
         <is>
           <t>Failing Tests</t>
         </is>
       </c>
-    </row>
-    <row r="18" ht="15" customHeight="1">
-      <c r="A18" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="B18" s="16" t="inlineStr">
-        <is>
-          <t>WIFI_TX-2412-HT20_MCS7-13</t>
-        </is>
-      </c>
-      <c r="C18" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="D18" s="7" t="inlineStr">
-        <is>
-          <t>25.00%</t>
-        </is>
-      </c>
-      <c r="E18" s="7" t="inlineStr">
-        <is>
-          <t>ITJS-D24F-SMT01-CWB-04</t>
-        </is>
-      </c>
-      <c r="F18" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G18" s="17" t="inlineStr"/>
-    </row>
-    <row r="19" ht="15" customHeight="1">
-      <c r="A19" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="B19" s="16" t="inlineStr">
-        <is>
-          <t>WIFI_TX-2412-OFDM-54M-14</t>
-        </is>
-      </c>
-      <c r="C19" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="D19" s="7" t="inlineStr">
-        <is>
-          <t>25.00%</t>
-        </is>
-      </c>
-      <c r="E19" s="7" t="inlineStr">
-        <is>
-          <t>ITJS-D24F-SMT01-CWB-05</t>
-        </is>
-      </c>
-      <c r="F19" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G19" s="17" t="inlineStr"/>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="B20" s="16" t="inlineStr">
+        <is>
+          <t>WIFI_TX-2412-HT20_MCS7-13</t>
+        </is>
+      </c>
+      <c r="C20" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D20" s="7" t="inlineStr">
+        <is>
+          <t>20.00%</t>
+        </is>
+      </c>
+      <c r="E20" s="7" t="inlineStr">
+        <is>
+          <t>ITJS-D24F-SMT01-CWB-04</t>
+        </is>
+      </c>
+      <c r="F20" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G20" s="17" t="inlineStr"/>
+    </row>
+    <row r="21" ht="15" customHeight="1">
+      <c r="A21" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="B21" s="16" t="inlineStr">
+        <is>
+          <t>WIFI_TX-2412-OFDM-54M-14</t>
+        </is>
+      </c>
+      <c r="C21" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D21" s="7" t="inlineStr">
+        <is>
+          <t>20.00%</t>
+        </is>
+      </c>
+      <c r="E21" s="7" t="inlineStr">
+        <is>
+          <t>ITJS-D24F-SMT01-CWB-05</t>
+        </is>
+      </c>
+      <c r="F21" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G21" s="17" t="inlineStr"/>
+    </row>
+    <row r="22" ht="15" customHeight="1">
+      <c r="A22" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="B20" s="16" t="inlineStr">
+      <c r="B22" s="16" t="inlineStr">
         <is>
           <t>WIFI_TX-5180-HT20_MCS7-12</t>
         </is>
       </c>
-      <c r="C20" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="D20" s="7" t="inlineStr">
-        <is>
-          <t>25.00%</t>
-        </is>
-      </c>
-      <c r="E20" s="7" t="inlineStr">
+      <c r="C22" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D22" s="7" t="inlineStr">
+        <is>
+          <t>20.00%</t>
+        </is>
+      </c>
+      <c r="E22" s="7" t="inlineStr">
         <is>
           <t>ITJS-D24F-SMT01-CWB-01</t>
         </is>
       </c>
-      <c r="F20" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G20" s="17" t="inlineStr"/>
-    </row>
-    <row r="21" ht="15" customHeight="1"/>
+      <c r="F22" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G22" s="17" t="inlineStr"/>
+    </row>
+    <row r="23" ht="15" customHeight="1"/>
   </sheetData>
   <mergeCells count="6">
     <mergeCell ref="A4:B4"/>

--- a/T11_CWB.xlsx
+++ b/T11_CWB.xlsx
@@ -539,7 +539,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R30"/>
+  <dimension ref="A1:R31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -611,17 +611,17 @@
       <c r="B4" s="3" t="n"/>
       <c r="C4" s="5" t="inlineStr">
         <is>
+          <t>V1.0.3.7</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
           <t>V1.0.4.1</t>
         </is>
       </c>
-      <c r="D4" s="5" t="inlineStr">
+      <c r="E4" s="5" t="inlineStr">
         <is>
           <t>V1.0.4.2</t>
-        </is>
-      </c>
-      <c r="E4" s="5" t="inlineStr">
-        <is>
-          <t>V1.0.3.7</t>
         </is>
       </c>
     </row>
@@ -986,20 +986,20 @@
       </c>
       <c r="B23" s="16" t="inlineStr">
         <is>
-          <t>WIFI_TX-2412-OFDM-54M-14</t>
+          <t>WIFI_RX-2412-HT20_MCS7--70</t>
         </is>
       </c>
       <c r="C23" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D23" s="7" t="inlineStr">
         <is>
-          <t>13.33%</t>
+          <t>6.67%</t>
         </is>
       </c>
       <c r="E23" s="7" t="inlineStr">
         <is>
-          <t>ITJS-D24F-SMT01-CWB-02</t>
+          <t>ITJS-D24F-SMT01-CWB-06</t>
         </is>
       </c>
       <c r="F23" s="7" t="n">
@@ -1008,27 +1008,39 @@
       <c r="G23" s="17" t="inlineStr"/>
     </row>
     <row r="24" ht="15" customHeight="1">
-      <c r="A24" s="19" t="n"/>
-      <c r="B24" s="19" t="n"/>
-      <c r="C24" s="19" t="n"/>
-      <c r="D24" s="19" t="n"/>
+      <c r="A24" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="B24" s="16" t="inlineStr">
+        <is>
+          <t>WIFI_TX-2412-HT20_MCS7-13</t>
+        </is>
+      </c>
+      <c r="C24" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D24" s="7" t="inlineStr">
+        <is>
+          <t>6.67%</t>
+        </is>
+      </c>
       <c r="E24" s="7" t="inlineStr">
         <is>
-          <t>ITJS-D24F-SMT01-CWB-05</t>
+          <t>ITJS-D24F-SMT01-CWB-04</t>
         </is>
       </c>
       <c r="F24" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="G24" s="19" t="n"/>
+      <c r="G24" s="17" t="inlineStr"/>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" s="7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B25" s="16" t="inlineStr">
         <is>
-          <t>WIFI_RX-2412-HT20_MCS7--70</t>
+          <t>WIFI_TX-2412-OFDM-54M-14</t>
         </is>
       </c>
       <c r="C25" s="7" t="n">
@@ -1041,7 +1053,7 @@
       </c>
       <c r="E25" s="7" t="inlineStr">
         <is>
-          <t>ITJS-D24F-SMT01-CWB-06</t>
+          <t>ITJS-D24F-SMT01-CWB-02</t>
         </is>
       </c>
       <c r="F25" s="7" t="n">
@@ -1051,129 +1063,127 @@
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" s="7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B26" s="16" t="inlineStr">
         <is>
+          <t>WIFI_TX-2442-OFDM-54M-14</t>
+        </is>
+      </c>
+      <c r="C26" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D26" s="7" t="inlineStr">
+        <is>
+          <t>6.67%</t>
+        </is>
+      </c>
+      <c r="E26" s="7" t="inlineStr">
+        <is>
+          <t>ITJS-D24F-SMT01-CWB-02</t>
+        </is>
+      </c>
+      <c r="F26" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G26" s="17" t="inlineStr"/>
+    </row>
+    <row r="27" ht="15" customHeight="1"/>
+    <row r="28" ht="15" customHeight="1"/>
+    <row r="29" ht="15" customHeight="1">
+      <c r="A29" s="15" t="inlineStr">
+        <is>
+          <t>NO.</t>
+        </is>
+      </c>
+      <c r="B29" s="15" t="inlineStr">
+        <is>
+          <t>Three FAIL Type</t>
+        </is>
+      </c>
+      <c r="C29" s="15" t="inlineStr">
+        <is>
+          <t>FAIL Count</t>
+        </is>
+      </c>
+      <c r="D29" s="15" t="inlineStr">
+        <is>
+          <t>Percentage</t>
+        </is>
+      </c>
+      <c r="E29" s="15" t="inlineStr">
+        <is>
+          <t>Station ID</t>
+        </is>
+      </c>
+      <c r="F29" s="15" t="inlineStr">
+        <is>
+          <t>Station Count</t>
+        </is>
+      </c>
+      <c r="G29" s="15" t="inlineStr">
+        <is>
+          <t>Failing Tests</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="15" customHeight="1">
+      <c r="A30" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B30" s="16" t="inlineStr">
+        <is>
           <t>WIFI_RX-2412-HT20_MCS7--75</t>
         </is>
       </c>
-      <c r="C26" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="D26" s="7" t="inlineStr">
+      <c r="C30" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D30" s="7" t="inlineStr">
         <is>
           <t>6.67%</t>
         </is>
       </c>
-      <c r="E26" s="7" t="inlineStr">
+      <c r="E30" s="7" t="inlineStr">
         <is>
           <t>ITJS-D24F-SMT01-CWB-06</t>
         </is>
       </c>
-      <c r="F26" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G26" s="17" t="inlineStr"/>
-    </row>
-    <row r="27" ht="15" customHeight="1">
-      <c r="A27" s="7" t="n">
-        <v>5</v>
-      </c>
-      <c r="B27" s="16" t="inlineStr">
-        <is>
-          <t>WIFI_TX-2412-HT20_MCS7-13</t>
-        </is>
-      </c>
-      <c r="C27" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="D27" s="7" t="inlineStr">
+      <c r="F30" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G30" s="17" t="inlineStr"/>
+    </row>
+    <row r="31" ht="15" customHeight="1">
+      <c r="A31" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="B31" s="16" t="inlineStr">
+        <is>
+          <t>WIFI_TX-2412-OFDM-54M-14</t>
+        </is>
+      </c>
+      <c r="C31" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D31" s="7" t="inlineStr">
         <is>
           <t>6.67%</t>
         </is>
       </c>
-      <c r="E27" s="7" t="inlineStr">
-        <is>
-          <t>ITJS-D24F-SMT01-CWB-04</t>
-        </is>
-      </c>
-      <c r="F27" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G27" s="17" t="inlineStr"/>
-    </row>
-    <row r="28" ht="15" customHeight="1">
-      <c r="A28" s="7" t="n">
-        <v>6</v>
-      </c>
-      <c r="B28" s="16" t="inlineStr">
-        <is>
-          <t>WIFI_TX-2442-OFDM-54M-14</t>
-        </is>
-      </c>
-      <c r="C28" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="D28" s="7" t="inlineStr">
-        <is>
-          <t>6.67%</t>
-        </is>
-      </c>
-      <c r="E28" s="7" t="inlineStr">
-        <is>
-          <t>ITJS-D24F-SMT01-CWB-02</t>
-        </is>
-      </c>
-      <c r="F28" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G28" s="17" t="inlineStr"/>
-    </row>
-    <row r="29" ht="15" customHeight="1"/>
-    <row r="30" ht="15" customHeight="1">
-      <c r="A30" s="15" t="inlineStr">
-        <is>
-          <t>NO.</t>
-        </is>
-      </c>
-      <c r="B30" s="15" t="inlineStr">
-        <is>
-          <t>Fail Type</t>
-        </is>
-      </c>
-      <c r="C30" s="15" t="inlineStr">
-        <is>
-          <t>Fail Count</t>
-        </is>
-      </c>
-      <c r="D30" s="15" t="inlineStr">
-        <is>
-          <t>Percentage</t>
-        </is>
-      </c>
-      <c r="E30" s="15" t="inlineStr">
-        <is>
-          <t>Station ID</t>
-        </is>
-      </c>
-      <c r="F30" s="15" t="inlineStr">
-        <is>
-          <t>Station Count</t>
-        </is>
-      </c>
-      <c r="G30" s="15" t="inlineStr">
-        <is>
-          <t>Failing Tests</t>
-        </is>
-      </c>
+      <c r="E31" s="7" t="inlineStr">
+        <is>
+          <t>ITJS-D24F-SMT01-CWB-05</t>
+        </is>
+      </c>
+      <c r="F31" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G31" s="17" t="inlineStr"/>
     </row>
   </sheetData>
-  <mergeCells count="16">
+  <mergeCells count="11">
     <mergeCell ref="A4:B4"/>
-    <mergeCell ref="B23:B24"/>
-    <mergeCell ref="C23:C24"/>
-    <mergeCell ref="G23:G24"/>
     <mergeCell ref="B20:B22"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="C20:C22"/>
@@ -1181,8 +1191,6 @@
     <mergeCell ref="A5:B5"/>
     <mergeCell ref="D20:D22"/>
     <mergeCell ref="G20:G22"/>
-    <mergeCell ref="A23:A24"/>
-    <mergeCell ref="D23:D24"/>
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A6:B6"/>
@@ -1197,7 +1205,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H22"/>
+  <dimension ref="A1:H25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -1264,12 +1272,12 @@
       <c r="B4" s="3" t="n"/>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>V1.0.4.1</t>
+          <t>V1.0.3.7</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>V1.0.4.1</t>
+          <t>V1.0.3.7</t>
         </is>
       </c>
     </row>
@@ -1530,55 +1538,93 @@
       </c>
       <c r="B21" s="16" t="inlineStr">
         <is>
+          <t>WIFI_TX-2412-OFDM-54M-14</t>
+        </is>
+      </c>
+      <c r="C21" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D21" s="7" t="inlineStr">
+        <is>
+          <t>16.67%</t>
+        </is>
+      </c>
+      <c r="E21" s="7" t="inlineStr">
+        <is>
+          <t>ITJS-D24F-SMT01-CWB-02</t>
+        </is>
+      </c>
+      <c r="F21" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G21" s="17" t="inlineStr"/>
+    </row>
+    <row r="22" ht="15" customHeight="1"/>
+    <row r="23" ht="15" customHeight="1"/>
+    <row r="24" ht="15" customHeight="1">
+      <c r="A24" s="15" t="inlineStr">
+        <is>
+          <t>NO.</t>
+        </is>
+      </c>
+      <c r="B24" s="15" t="inlineStr">
+        <is>
+          <t>Three FAIL Type</t>
+        </is>
+      </c>
+      <c r="C24" s="15" t="inlineStr">
+        <is>
+          <t>FAIL Count</t>
+        </is>
+      </c>
+      <c r="D24" s="15" t="inlineStr">
+        <is>
+          <t>Percentage</t>
+        </is>
+      </c>
+      <c r="E24" s="15" t="inlineStr">
+        <is>
+          <t>Station ID</t>
+        </is>
+      </c>
+      <c r="F24" s="15" t="inlineStr">
+        <is>
+          <t>Station Count</t>
+        </is>
+      </c>
+      <c r="G24" s="15" t="inlineStr">
+        <is>
+          <t>Failing Tests</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="15" customHeight="1">
+      <c r="A25" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="B25" s="16" t="inlineStr">
+        <is>
           <t>WIFI_RX-2412-HT20_MCS7--75</t>
         </is>
       </c>
-      <c r="C21" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="D21" s="7" t="inlineStr">
+      <c r="C25" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D25" s="7" t="inlineStr">
         <is>
           <t>16.67%</t>
         </is>
       </c>
-      <c r="E21" s="7" t="inlineStr">
+      <c r="E25" s="7" t="inlineStr">
         <is>
           <t>ITJS-D24F-SMT01-CWB-06</t>
         </is>
       </c>
-      <c r="F21" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G21" s="17" t="inlineStr"/>
-    </row>
-    <row r="22" ht="15" customHeight="1">
-      <c r="A22" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="B22" s="16" t="inlineStr">
-        <is>
-          <t>WIFI_TX-2412-OFDM-54M-14</t>
-        </is>
-      </c>
-      <c r="C22" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="D22" s="7" t="inlineStr">
-        <is>
-          <t>16.67%</t>
-        </is>
-      </c>
-      <c r="E22" s="7" t="inlineStr">
-        <is>
-          <t>ITJS-D24F-SMT01-CWB-02</t>
-        </is>
-      </c>
-      <c r="F22" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G22" s="17" t="inlineStr"/>
-    </row>
-    <row r="23" ht="15" customHeight="1"/>
+      <c r="F25" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G25" s="17" t="inlineStr"/>
+    </row>
   </sheetData>
   <mergeCells count="6">
     <mergeCell ref="A4:B4"/>
@@ -1598,7 +1644,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H22"/>
+  <dimension ref="A1:H25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -1968,6 +2014,44 @@
       <c r="G22" s="17" t="inlineStr"/>
     </row>
     <row r="23" ht="15" customHeight="1"/>
+    <row r="24" ht="15" customHeight="1"/>
+    <row r="25" ht="15" customHeight="1">
+      <c r="A25" s="15" t="inlineStr">
+        <is>
+          <t>NO.</t>
+        </is>
+      </c>
+      <c r="B25" s="15" t="inlineStr">
+        <is>
+          <t>Three FAIL Type</t>
+        </is>
+      </c>
+      <c r="C25" s="15" t="inlineStr">
+        <is>
+          <t>FAIL Count</t>
+        </is>
+      </c>
+      <c r="D25" s="15" t="inlineStr">
+        <is>
+          <t>Percentage</t>
+        </is>
+      </c>
+      <c r="E25" s="15" t="inlineStr">
+        <is>
+          <t>Station ID</t>
+        </is>
+      </c>
+      <c r="F25" s="15" t="inlineStr">
+        <is>
+          <t>Station Count</t>
+        </is>
+      </c>
+      <c r="G25" s="15" t="inlineStr">
+        <is>
+          <t>Failing Tests</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="11">
     <mergeCell ref="A4:B4"/>
@@ -1992,7 +2076,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H22"/>
+  <dimension ref="A1:H25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -2277,55 +2361,93 @@
       </c>
       <c r="B21" s="16" t="inlineStr">
         <is>
+          <t>WIFI_TX-5180-HT20_MCS7-12</t>
+        </is>
+      </c>
+      <c r="C21" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D21" s="7" t="inlineStr">
+        <is>
+          <t>20.00%</t>
+        </is>
+      </c>
+      <c r="E21" s="7" t="inlineStr">
+        <is>
+          <t>ITJS-D24F-SMT01-CWB-01</t>
+        </is>
+      </c>
+      <c r="F21" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G21" s="17" t="inlineStr"/>
+    </row>
+    <row r="22" ht="15" customHeight="1"/>
+    <row r="23" ht="15" customHeight="1"/>
+    <row r="24" ht="15" customHeight="1">
+      <c r="A24" s="15" t="inlineStr">
+        <is>
+          <t>NO.</t>
+        </is>
+      </c>
+      <c r="B24" s="15" t="inlineStr">
+        <is>
+          <t>Three FAIL Type</t>
+        </is>
+      </c>
+      <c r="C24" s="15" t="inlineStr">
+        <is>
+          <t>FAIL Count</t>
+        </is>
+      </c>
+      <c r="D24" s="15" t="inlineStr">
+        <is>
+          <t>Percentage</t>
+        </is>
+      </c>
+      <c r="E24" s="15" t="inlineStr">
+        <is>
+          <t>Station ID</t>
+        </is>
+      </c>
+      <c r="F24" s="15" t="inlineStr">
+        <is>
+          <t>Station Count</t>
+        </is>
+      </c>
+      <c r="G24" s="15" t="inlineStr">
+        <is>
+          <t>Failing Tests</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="15" customHeight="1">
+      <c r="A25" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="B25" s="16" t="inlineStr">
+        <is>
           <t>WIFI_TX-2412-OFDM-54M-14</t>
         </is>
       </c>
-      <c r="C21" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="D21" s="7" t="inlineStr">
+      <c r="C25" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D25" s="7" t="inlineStr">
         <is>
           <t>20.00%</t>
         </is>
       </c>
-      <c r="E21" s="7" t="inlineStr">
+      <c r="E25" s="7" t="inlineStr">
         <is>
           <t>ITJS-D24F-SMT01-CWB-05</t>
         </is>
       </c>
-      <c r="F21" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G21" s="17" t="inlineStr"/>
-    </row>
-    <row r="22" ht="15" customHeight="1">
-      <c r="A22" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="B22" s="16" t="inlineStr">
-        <is>
-          <t>WIFI_TX-5180-HT20_MCS7-12</t>
-        </is>
-      </c>
-      <c r="C22" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="D22" s="7" t="inlineStr">
-        <is>
-          <t>20.00%</t>
-        </is>
-      </c>
-      <c r="E22" s="7" t="inlineStr">
-        <is>
-          <t>ITJS-D24F-SMT01-CWB-01</t>
-        </is>
-      </c>
-      <c r="F22" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G22" s="17" t="inlineStr"/>
-    </row>
-    <row r="23" ht="15" customHeight="1"/>
+      <c r="F25" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G25" s="17" t="inlineStr"/>
+    </row>
   </sheetData>
   <mergeCells count="6">
     <mergeCell ref="A4:B4"/>

--- a/T11_CWB.xlsx
+++ b/T11_CWB.xlsx
@@ -20,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -31,9 +31,6 @@
     <font>
       <b val="1"/>
       <sz val="22"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="5">
@@ -129,7 +126,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -161,9 +158,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="10" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -539,7 +533,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R31"/>
+  <dimension ref="A1:H32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -611,17 +605,17 @@
       <c r="B4" s="3" t="n"/>
       <c r="C4" s="5" t="inlineStr">
         <is>
+          <t>V1.0.4.1</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>V1.0.4.2</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
           <t>V1.0.3.7</t>
-        </is>
-      </c>
-      <c r="D4" s="5" t="inlineStr">
-        <is>
-          <t>V1.0.4.1</t>
-        </is>
-      </c>
-      <c r="E4" s="5" t="inlineStr">
-        <is>
-          <t>V1.0.4.2</t>
         </is>
       </c>
     </row>
@@ -865,59 +859,46 @@
           <t>20.00%</t>
         </is>
       </c>
-      <c r="F15" s="11" t="n"/>
-      <c r="G15" s="11" t="n"/>
-      <c r="H15" s="11" t="n"/>
-      <c r="I15" s="11" t="n"/>
-      <c r="J15" s="11" t="n"/>
-      <c r="K15" s="11" t="n"/>
-      <c r="L15" s="11" t="n"/>
-      <c r="M15" s="11" t="n"/>
-      <c r="N15" s="11" t="n"/>
-      <c r="O15" s="11" t="n"/>
-      <c r="P15" s="11" t="n"/>
-      <c r="Q15" s="11" t="n"/>
-      <c r="R15" s="11" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="7" t="inlineStr">
+      <c r="A18" s="5" t="inlineStr">
         <is>
           <t>Retest OK Quantity</t>
         </is>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
-      <c r="A19" s="15" t="inlineStr">
+      <c r="A19" s="5" t="inlineStr">
         <is>
           <t>NO.</t>
         </is>
       </c>
-      <c r="B19" s="15" t="inlineStr">
+      <c r="B19" s="5" t="inlineStr">
         <is>
           <t>Retest Type</t>
         </is>
       </c>
-      <c r="C19" s="15" t="inlineStr">
+      <c r="C19" s="5" t="inlineStr">
         <is>
           <t>Retest Count</t>
         </is>
       </c>
-      <c r="D19" s="15" t="inlineStr">
+      <c r="D19" s="5" t="inlineStr">
         <is>
           <t>Percentage</t>
         </is>
       </c>
-      <c r="E19" s="15" t="inlineStr">
+      <c r="E19" s="5" t="inlineStr">
         <is>
           <t>Station ID</t>
         </is>
       </c>
-      <c r="F19" s="15" t="inlineStr">
+      <c r="F19" s="5" t="inlineStr">
         <is>
           <t>Station Count</t>
         </is>
       </c>
-      <c r="G19" s="15" t="inlineStr">
+      <c r="G19" s="5" t="inlineStr">
         <is>
           <t>Failing Tests</t>
         </is>
@@ -927,7 +908,7 @@
       <c r="A20" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="B20" s="16" t="inlineStr">
+      <c r="B20" s="15" t="inlineStr">
         <is>
           <t>WIFI_TX-5180-HT20_MCS7-12</t>
         </is>
@@ -948,13 +929,13 @@
       <c r="F20" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="G20" s="17" t="inlineStr"/>
+      <c r="G20" s="16" t="inlineStr"/>
     </row>
     <row r="21" ht="15" customHeight="1">
-      <c r="A21" s="18" t="n"/>
-      <c r="B21" s="18" t="n"/>
-      <c r="C21" s="18" t="n"/>
-      <c r="D21" s="18" t="n"/>
+      <c r="A21" s="17" t="n"/>
+      <c r="B21" s="17" t="n"/>
+      <c r="C21" s="17" t="n"/>
+      <c r="D21" s="17" t="n"/>
       <c r="E21" s="7" t="inlineStr">
         <is>
           <t>ITJS-D24F-SMT01-CWB-02</t>
@@ -963,13 +944,13 @@
       <c r="F21" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="G21" s="18" t="n"/>
+      <c r="G21" s="17" t="n"/>
     </row>
     <row r="22" ht="15" customHeight="1">
-      <c r="A22" s="19" t="n"/>
-      <c r="B22" s="19" t="n"/>
-      <c r="C22" s="19" t="n"/>
-      <c r="D22" s="19" t="n"/>
+      <c r="A22" s="18" t="n"/>
+      <c r="B22" s="18" t="n"/>
+      <c r="C22" s="18" t="n"/>
+      <c r="D22" s="18" t="n"/>
       <c r="E22" s="7" t="inlineStr">
         <is>
           <t>ITJS-D24F-SMT01-CWB-06</t>
@@ -978,13 +959,13 @@
       <c r="F22" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="G22" s="19" t="n"/>
+      <c r="G22" s="18" t="n"/>
     </row>
     <row r="23" ht="15" customHeight="1">
       <c r="A23" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="B23" s="16" t="inlineStr">
+      <c r="B23" s="15" t="inlineStr">
         <is>
           <t>WIFI_RX-2412-HT20_MCS7--70</t>
         </is>
@@ -1005,13 +986,13 @@
       <c r="F23" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="G23" s="17" t="inlineStr"/>
+      <c r="G23" s="16" t="inlineStr"/>
     </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="B24" s="16" t="inlineStr">
+      <c r="B24" s="15" t="inlineStr">
         <is>
           <t>WIFI_TX-2412-HT20_MCS7-13</t>
         </is>
@@ -1032,13 +1013,13 @@
       <c r="F24" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="G24" s="17" t="inlineStr"/>
+      <c r="G24" s="16" t="inlineStr"/>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="B25" s="16" t="inlineStr">
+      <c r="B25" s="15" t="inlineStr">
         <is>
           <t>WIFI_TX-2412-OFDM-54M-14</t>
         </is>
@@ -1059,13 +1040,13 @@
       <c r="F25" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="G25" s="17" t="inlineStr"/>
+      <c r="G25" s="16" t="inlineStr"/>
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="B26" s="16" t="inlineStr">
+      <c r="B26" s="15" t="inlineStr">
         <is>
           <t>WIFI_TX-2442-OFDM-54M-14</t>
         </is>
@@ -1086,100 +1067,107 @@
       <c r="F26" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="G26" s="17" t="inlineStr"/>
+      <c r="G26" s="16" t="inlineStr"/>
     </row>
     <row r="27" ht="15" customHeight="1"/>
     <row r="28" ht="15" customHeight="1"/>
     <row r="29" ht="15" customHeight="1">
-      <c r="A29" s="15" t="inlineStr">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>Test Fail Quantity</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="15" customHeight="1">
+      <c r="A30" s="5" t="inlineStr">
         <is>
           <t>NO.</t>
         </is>
       </c>
-      <c r="B29" s="15" t="inlineStr">
-        <is>
-          <t>Three FAIL Type</t>
-        </is>
-      </c>
-      <c r="C29" s="15" t="inlineStr">
-        <is>
-          <t>FAIL Count</t>
-        </is>
-      </c>
-      <c r="D29" s="15" t="inlineStr">
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>Fail Type</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>Fail Count</t>
+        </is>
+      </c>
+      <c r="D30" s="5" t="inlineStr">
         <is>
           <t>Percentage</t>
         </is>
       </c>
-      <c r="E29" s="15" t="inlineStr">
+      <c r="E30" s="5" t="inlineStr">
         <is>
           <t>Station ID</t>
         </is>
       </c>
-      <c r="F29" s="15" t="inlineStr">
+      <c r="F30" s="5" t="inlineStr">
         <is>
           <t>Station Count</t>
         </is>
       </c>
-      <c r="G29" s="15" t="inlineStr">
+      <c r="G30" s="5" t="inlineStr">
         <is>
           <t>Failing Tests</t>
         </is>
       </c>
-    </row>
-    <row r="30" ht="15" customHeight="1">
-      <c r="A30" s="7" t="n">
-        <v>6</v>
-      </c>
-      <c r="B30" s="16" t="inlineStr">
-        <is>
-          <t>WIFI_RX-2412-HT20_MCS7--75</t>
-        </is>
-      </c>
-      <c r="C30" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="D30" s="7" t="inlineStr">
-        <is>
-          <t>6.67%</t>
-        </is>
-      </c>
-      <c r="E30" s="7" t="inlineStr">
-        <is>
-          <t>ITJS-D24F-SMT01-CWB-06</t>
-        </is>
-      </c>
-      <c r="F30" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G30" s="17" t="inlineStr"/>
     </row>
     <row r="31" ht="15" customHeight="1">
       <c r="A31" s="7" t="n">
-        <v>7</v>
-      </c>
-      <c r="B31" s="16" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="B31" s="15" t="inlineStr">
+        <is>
+          <t>WIFI_RX-2412-HT20_MCS7--75</t>
+        </is>
+      </c>
+      <c r="C31" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D31" s="7" t="inlineStr">
+        <is>
+          <t>6.67%</t>
+        </is>
+      </c>
+      <c r="E31" s="7" t="inlineStr">
+        <is>
+          <t>ITJS-D24F-SMT01-CWB-06</t>
+        </is>
+      </c>
+      <c r="F31" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G31" s="16" t="inlineStr"/>
+    </row>
+    <row r="32" ht="15" customHeight="1">
+      <c r="A32" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="B32" s="15" t="inlineStr">
         <is>
           <t>WIFI_TX-2412-OFDM-54M-14</t>
         </is>
       </c>
-      <c r="C31" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="D31" s="7" t="inlineStr">
+      <c r="C32" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D32" s="7" t="inlineStr">
         <is>
           <t>6.67%</t>
         </is>
       </c>
-      <c r="E31" s="7" t="inlineStr">
+      <c r="E32" s="7" t="inlineStr">
         <is>
           <t>ITJS-D24F-SMT01-CWB-05</t>
         </is>
       </c>
-      <c r="F31" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G31" s="17" t="inlineStr"/>
+      <c r="F32" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G32" s="16" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="11">
@@ -1205,7 +1193,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H25"/>
+  <dimension ref="A1:H26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -1272,12 +1260,12 @@
       <c r="B4" s="3" t="n"/>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>V1.0.3.7</t>
+          <t>V1.0.4.1</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>V1.0.3.7</t>
+          <t>V1.0.4.1</t>
         </is>
       </c>
     </row>
@@ -1462,44 +1450,44 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="7" t="inlineStr">
+      <c r="A18" s="5" t="inlineStr">
         <is>
           <t>Retest OK Quantity</t>
         </is>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
-      <c r="A19" s="15" t="inlineStr">
+      <c r="A19" s="5" t="inlineStr">
         <is>
           <t>NO.</t>
         </is>
       </c>
-      <c r="B19" s="15" t="inlineStr">
+      <c r="B19" s="5" t="inlineStr">
         <is>
           <t>Retest Type</t>
         </is>
       </c>
-      <c r="C19" s="15" t="inlineStr">
+      <c r="C19" s="5" t="inlineStr">
         <is>
           <t>Retest Count</t>
         </is>
       </c>
-      <c r="D19" s="15" t="inlineStr">
+      <c r="D19" s="5" t="inlineStr">
         <is>
           <t>Percentage</t>
         </is>
       </c>
-      <c r="E19" s="15" t="inlineStr">
+      <c r="E19" s="5" t="inlineStr">
         <is>
           <t>Station ID</t>
         </is>
       </c>
-      <c r="F19" s="15" t="inlineStr">
+      <c r="F19" s="5" t="inlineStr">
         <is>
           <t>Station Count</t>
         </is>
       </c>
-      <c r="G19" s="15" t="inlineStr">
+      <c r="G19" s="5" t="inlineStr">
         <is>
           <t>Failing Tests</t>
         </is>
@@ -1509,7 +1497,7 @@
       <c r="A20" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="B20" s="16" t="inlineStr">
+      <c r="B20" s="15" t="inlineStr">
         <is>
           <t>WIFI_RX-2412-HT20_MCS7--70</t>
         </is>
@@ -1530,13 +1518,13 @@
       <c r="F20" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="G20" s="17" t="inlineStr"/>
+      <c r="G20" s="16" t="inlineStr"/>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="B21" s="16" t="inlineStr">
+      <c r="B21" s="15" t="inlineStr">
         <is>
           <t>WIFI_TX-2412-OFDM-54M-14</t>
         </is>
@@ -1557,73 +1545,80 @@
       <c r="F21" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="G21" s="17" t="inlineStr"/>
+      <c r="G21" s="16" t="inlineStr"/>
     </row>
     <row r="22" ht="15" customHeight="1"/>
     <row r="23" ht="15" customHeight="1"/>
     <row r="24" ht="15" customHeight="1">
-      <c r="A24" s="15" t="inlineStr">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>Test Fail Quantity</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="15" customHeight="1">
+      <c r="A25" s="5" t="inlineStr">
         <is>
           <t>NO.</t>
         </is>
       </c>
-      <c r="B24" s="15" t="inlineStr">
-        <is>
-          <t>Three FAIL Type</t>
-        </is>
-      </c>
-      <c r="C24" s="15" t="inlineStr">
-        <is>
-          <t>FAIL Count</t>
-        </is>
-      </c>
-      <c r="D24" s="15" t="inlineStr">
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>Fail Type</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>Fail Count</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="inlineStr">
         <is>
           <t>Percentage</t>
         </is>
       </c>
-      <c r="E24" s="15" t="inlineStr">
+      <c r="E25" s="5" t="inlineStr">
         <is>
           <t>Station ID</t>
         </is>
       </c>
-      <c r="F24" s="15" t="inlineStr">
+      <c r="F25" s="5" t="inlineStr">
         <is>
           <t>Station Count</t>
         </is>
       </c>
-      <c r="G24" s="15" t="inlineStr">
+      <c r="G25" s="5" t="inlineStr">
         <is>
           <t>Failing Tests</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="15" customHeight="1">
-      <c r="A25" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="B25" s="16" t="inlineStr">
+    <row r="26" ht="15" customHeight="1">
+      <c r="A26" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="B26" s="15" t="inlineStr">
         <is>
           <t>WIFI_RX-2412-HT20_MCS7--75</t>
         </is>
       </c>
-      <c r="C25" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="D25" s="7" t="inlineStr">
+      <c r="C26" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D26" s="7" t="inlineStr">
         <is>
           <t>16.67%</t>
         </is>
       </c>
-      <c r="E25" s="7" t="inlineStr">
+      <c r="E26" s="7" t="inlineStr">
         <is>
           <t>ITJS-D24F-SMT01-CWB-06</t>
         </is>
       </c>
-      <c r="F25" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G25" s="17" t="inlineStr"/>
+      <c r="F26" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G26" s="16" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="6">
@@ -1644,7 +1639,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H25"/>
+  <dimension ref="A1:H26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -1901,44 +1896,44 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="7" t="inlineStr">
+      <c r="A18" s="5" t="inlineStr">
         <is>
           <t>Retest OK Quantity</t>
         </is>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
-      <c r="A19" s="15" t="inlineStr">
+      <c r="A19" s="5" t="inlineStr">
         <is>
           <t>NO.</t>
         </is>
       </c>
-      <c r="B19" s="15" t="inlineStr">
+      <c r="B19" s="5" t="inlineStr">
         <is>
           <t>Retest Type</t>
         </is>
       </c>
-      <c r="C19" s="15" t="inlineStr">
+      <c r="C19" s="5" t="inlineStr">
         <is>
           <t>Retest Count</t>
         </is>
       </c>
-      <c r="D19" s="15" t="inlineStr">
+      <c r="D19" s="5" t="inlineStr">
         <is>
           <t>Percentage</t>
         </is>
       </c>
-      <c r="E19" s="15" t="inlineStr">
+      <c r="E19" s="5" t="inlineStr">
         <is>
           <t>Station ID</t>
         </is>
       </c>
-      <c r="F19" s="15" t="inlineStr">
+      <c r="F19" s="5" t="inlineStr">
         <is>
           <t>Station Count</t>
         </is>
       </c>
-      <c r="G19" s="15" t="inlineStr">
+      <c r="G19" s="5" t="inlineStr">
         <is>
           <t>Failing Tests</t>
         </is>
@@ -1948,7 +1943,7 @@
       <c r="A20" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="B20" s="16" t="inlineStr">
+      <c r="B20" s="15" t="inlineStr">
         <is>
           <t>WIFI_TX-5180-HT20_MCS7-12</t>
         </is>
@@ -1969,13 +1964,13 @@
       <c r="F20" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="G20" s="17" t="inlineStr"/>
+      <c r="G20" s="16" t="inlineStr"/>
     </row>
     <row r="21" ht="15" customHeight="1">
-      <c r="A21" s="19" t="n"/>
-      <c r="B21" s="19" t="n"/>
-      <c r="C21" s="19" t="n"/>
-      <c r="D21" s="19" t="n"/>
+      <c r="A21" s="18" t="n"/>
+      <c r="B21" s="18" t="n"/>
+      <c r="C21" s="18" t="n"/>
+      <c r="D21" s="18" t="n"/>
       <c r="E21" s="7" t="inlineStr">
         <is>
           <t>ITJS-D24F-SMT01-CWB-06</t>
@@ -1984,13 +1979,13 @@
       <c r="F21" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="G21" s="19" t="n"/>
+      <c r="G21" s="18" t="n"/>
     </row>
     <row r="22" ht="15" customHeight="1">
       <c r="A22" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="B22" s="16" t="inlineStr">
+      <c r="B22" s="15" t="inlineStr">
         <is>
           <t>WIFI_TX-2442-OFDM-54M-14</t>
         </is>
@@ -2011,42 +2006,49 @@
       <c r="F22" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="G22" s="17" t="inlineStr"/>
+      <c r="G22" s="16" t="inlineStr"/>
     </row>
     <row r="23" ht="15" customHeight="1"/>
     <row r="24" ht="15" customHeight="1"/>
     <row r="25" ht="15" customHeight="1">
-      <c r="A25" s="15" t="inlineStr">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>Test Fail Quantity</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="15" customHeight="1">
+      <c r="A26" s="5" t="inlineStr">
         <is>
           <t>NO.</t>
         </is>
       </c>
-      <c r="B25" s="15" t="inlineStr">
-        <is>
-          <t>Three FAIL Type</t>
-        </is>
-      </c>
-      <c r="C25" s="15" t="inlineStr">
-        <is>
-          <t>FAIL Count</t>
-        </is>
-      </c>
-      <c r="D25" s="15" t="inlineStr">
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>Fail Type</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>Fail Count</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="inlineStr">
         <is>
           <t>Percentage</t>
         </is>
       </c>
-      <c r="E25" s="15" t="inlineStr">
+      <c r="E26" s="5" t="inlineStr">
         <is>
           <t>Station ID</t>
         </is>
       </c>
-      <c r="F25" s="15" t="inlineStr">
+      <c r="F26" s="5" t="inlineStr">
         <is>
           <t>Station Count</t>
         </is>
       </c>
-      <c r="G25" s="15" t="inlineStr">
+      <c r="G26" s="5" t="inlineStr">
         <is>
           <t>Failing Tests</t>
         </is>
@@ -2076,7 +2078,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H25"/>
+  <dimension ref="A1:H26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -2285,44 +2287,44 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="7" t="inlineStr">
+      <c r="A18" s="5" t="inlineStr">
         <is>
           <t>Retest OK Quantity</t>
         </is>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
-      <c r="A19" s="15" t="inlineStr">
+      <c r="A19" s="5" t="inlineStr">
         <is>
           <t>NO.</t>
         </is>
       </c>
-      <c r="B19" s="15" t="inlineStr">
+      <c r="B19" s="5" t="inlineStr">
         <is>
           <t>Retest Type</t>
         </is>
       </c>
-      <c r="C19" s="15" t="inlineStr">
+      <c r="C19" s="5" t="inlineStr">
         <is>
           <t>Retest Count</t>
         </is>
       </c>
-      <c r="D19" s="15" t="inlineStr">
+      <c r="D19" s="5" t="inlineStr">
         <is>
           <t>Percentage</t>
         </is>
       </c>
-      <c r="E19" s="15" t="inlineStr">
+      <c r="E19" s="5" t="inlineStr">
         <is>
           <t>Station ID</t>
         </is>
       </c>
-      <c r="F19" s="15" t="inlineStr">
+      <c r="F19" s="5" t="inlineStr">
         <is>
           <t>Station Count</t>
         </is>
       </c>
-      <c r="G19" s="15" t="inlineStr">
+      <c r="G19" s="5" t="inlineStr">
         <is>
           <t>Failing Tests</t>
         </is>
@@ -2332,7 +2334,7 @@
       <c r="A20" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="B20" s="16" t="inlineStr">
+      <c r="B20" s="15" t="inlineStr">
         <is>
           <t>WIFI_TX-2412-HT20_MCS7-13</t>
         </is>
@@ -2353,13 +2355,13 @@
       <c r="F20" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="G20" s="17" t="inlineStr"/>
+      <c r="G20" s="16" t="inlineStr"/>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="B21" s="16" t="inlineStr">
+      <c r="B21" s="15" t="inlineStr">
         <is>
           <t>WIFI_TX-5180-HT20_MCS7-12</t>
         </is>
@@ -2380,73 +2382,80 @@
       <c r="F21" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="G21" s="17" t="inlineStr"/>
+      <c r="G21" s="16" t="inlineStr"/>
     </row>
     <row r="22" ht="15" customHeight="1"/>
     <row r="23" ht="15" customHeight="1"/>
     <row r="24" ht="15" customHeight="1">
-      <c r="A24" s="15" t="inlineStr">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>Test Fail Quantity</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="15" customHeight="1">
+      <c r="A25" s="5" t="inlineStr">
         <is>
           <t>NO.</t>
         </is>
       </c>
-      <c r="B24" s="15" t="inlineStr">
-        <is>
-          <t>Three FAIL Type</t>
-        </is>
-      </c>
-      <c r="C24" s="15" t="inlineStr">
-        <is>
-          <t>FAIL Count</t>
-        </is>
-      </c>
-      <c r="D24" s="15" t="inlineStr">
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>Fail Type</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>Fail Count</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="inlineStr">
         <is>
           <t>Percentage</t>
         </is>
       </c>
-      <c r="E24" s="15" t="inlineStr">
+      <c r="E25" s="5" t="inlineStr">
         <is>
           <t>Station ID</t>
         </is>
       </c>
-      <c r="F24" s="15" t="inlineStr">
+      <c r="F25" s="5" t="inlineStr">
         <is>
           <t>Station Count</t>
         </is>
       </c>
-      <c r="G24" s="15" t="inlineStr">
+      <c r="G25" s="5" t="inlineStr">
         <is>
           <t>Failing Tests</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="15" customHeight="1">
-      <c r="A25" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="B25" s="16" t="inlineStr">
+    <row r="26" ht="15" customHeight="1">
+      <c r="A26" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="B26" s="15" t="inlineStr">
         <is>
           <t>WIFI_TX-2412-OFDM-54M-14</t>
         </is>
       </c>
-      <c r="C25" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="D25" s="7" t="inlineStr">
+      <c r="C26" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D26" s="7" t="inlineStr">
         <is>
           <t>20.00%</t>
         </is>
       </c>
-      <c r="E25" s="7" t="inlineStr">
+      <c r="E26" s="7" t="inlineStr">
         <is>
           <t>ITJS-D24F-SMT01-CWB-05</t>
         </is>
       </c>
-      <c r="F25" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G25" s="17" t="inlineStr"/>
+      <c r="F26" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G26" s="16" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="6">
